--- a/master/result/23_迷雾森林：真相追击/23_迷雾森林.xlsx
+++ b/master/result/23_迷雾森林：真相追击/23_迷雾森林.xlsx
@@ -397,621 +397,787 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:D55"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>verge</v>
       </c>
       <c r="B2" t="str">
-        <v>verge</v>
+        <v>/verge/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>边缘</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>immigrant</v>
       </c>
       <c r="B3" t="str">
-        <v>immigrant</v>
+        <v>/immigrant/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>移民</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>fragrant</v>
       </c>
       <c r="B4" t="str">
-        <v>fragrant</v>
+        <v>/fragrant/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>芬芳</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>cable</v>
       </c>
       <c r="B5" t="str">
-        <v>cable</v>
+        <v>/ˈkeɪbəl/</v>
       </c>
       <c r="C5" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>电报</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>porter</v>
       </c>
       <c r="B6" t="str">
-        <v>porter</v>
+        <v>/porter/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>门房</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>ground</v>
       </c>
       <c r="B7" t="str">
-        <v>ground</v>
+        <v>/ground/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>地面</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>mushroom</v>
       </c>
       <c r="B8" t="str">
-        <v>mushroom</v>
+        <v>/mushroom/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>蘑菇</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>tremendous</v>
       </c>
       <c r="B9" t="str">
-        <v>tremendous</v>
+        <v>/tremendous/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>巨大的</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>sequence</v>
       </c>
       <c r="B10" t="str">
-        <v>sequence</v>
+        <v>/sequence/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>顺序</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>gauge</v>
       </c>
       <c r="B11" t="str">
-        <v>gauge</v>
+        <v>/gauge/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>量表</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>rap</v>
       </c>
       <c r="B12" t="str">
-        <v>rap</v>
+        <v>/rap/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>叩击</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>primitive</v>
       </c>
       <c r="B13" t="str">
-        <v>primitive</v>
+        <v>/primitive/</v>
       </c>
       <c r="C13" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>原始</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>orderly</v>
       </c>
       <c r="B14" t="str">
-        <v>orderly</v>
+        <v>/orderly/</v>
       </c>
       <c r="C14" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>有序的</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>prey</v>
       </c>
       <c r="B15" t="str">
-        <v>prey</v>
+        <v>/prey/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>猎物</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>downstairs</v>
       </c>
       <c r="B16" t="str">
-        <v>downstairs</v>
+        <v>/downstairs/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>楼下</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>site</v>
       </c>
       <c r="B17" t="str">
-        <v>site</v>
+        <v>/site/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>地点</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>jazz</v>
       </c>
       <c r="B18" t="str">
-        <v>jazz</v>
+        <v>/jazz/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>爵士乐</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>cheque</v>
       </c>
       <c r="B19" t="str">
-        <v>cheque</v>
+        <v>/tʃek/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>支票</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>billion</v>
       </c>
       <c r="B20" t="str">
-        <v>billion</v>
+        <v>/billion/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>十亿</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>cause</v>
       </c>
       <c r="B21" t="str">
-        <v>cause</v>
+        <v>/kɔːz/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>原因</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>evade</v>
       </c>
       <c r="B22" t="str">
+        <v>/evade/</v>
+      </c>
+      <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
+        <v>逃避</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>trap</v>
+      </c>
+      <c r="B23" t="str">
+        <v>/trap/</v>
+      </c>
+      <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
+        <v>陷阱</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>truck</v>
+      </c>
+      <c r="B24" t="str">
+        <v>/truck/</v>
+      </c>
+      <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
+        <v>卡车</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>grab</v>
+      </c>
+      <c r="B25" t="str">
+        <v>/ɡræb/</v>
+      </c>
+      <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
+        <v>抓住</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>refuge</v>
+      </c>
+      <c r="B26" t="str">
+        <v>/refuge/</v>
+      </c>
+      <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>避难处</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>extra</v>
+      </c>
+      <c r="B27" t="str">
+        <v>/extra/</v>
+      </c>
+      <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
+        <v>额外</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>controversy</v>
+      </c>
+      <c r="B28" t="str">
+        <v>/ˈkɒntrəvɜːsi/</v>
+      </c>
+      <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>争论</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>excessive</v>
+      </c>
+      <c r="B29" t="str">
+        <v>/excessive/</v>
+      </c>
+      <c r="C29" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>过度的</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>realise</v>
+      </c>
+      <c r="B30" t="str">
+        <v>/realise/</v>
+      </c>
+      <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
+        <v>意识到</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>instruct</v>
+      </c>
+      <c r="B31" t="str">
+        <v>/instruct/</v>
+      </c>
+      <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
+        <v>指示</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>rim</v>
+      </c>
+      <c r="B32" t="str">
+        <v>/rim/</v>
+      </c>
+      <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
+        <v>边缘</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>grain</v>
+      </c>
+      <c r="B33" t="str">
+        <v>/grain/</v>
+      </c>
+      <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
+        <v>谷物</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>stereo</v>
+      </c>
+      <c r="B34" t="str">
+        <v>/stereo/</v>
+      </c>
+      <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
+        <v>音响</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>light</v>
+      </c>
+      <c r="B35" t="str">
+        <v>/laɪt/</v>
+      </c>
+      <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
+        <v>光</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
         <v>evade</v>
       </c>
-      <c r="C22" t="str">
-        <v>逃避</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="str">
-        <v>trap</v>
-      </c>
-      <c r="C23" t="str">
-        <v>陷阱</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="str">
-        <v>truck</v>
-      </c>
-      <c r="C24" t="str">
-        <v>卡车</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="str">
-        <v>grab</v>
-      </c>
-      <c r="C25" t="str">
-        <v>抓住</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="str">
-        <v>refuge</v>
-      </c>
-      <c r="C26" t="str">
-        <v>避难处</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="str">
-        <v>extra</v>
-      </c>
-      <c r="C27" t="str">
-        <v>额外</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="str">
-        <v>controversy</v>
-      </c>
-      <c r="C28" t="str">
-        <v>争论</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="str">
-        <v>excessive</v>
-      </c>
-      <c r="C29" t="str">
-        <v>过度的</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="str">
-        <v>realise</v>
-      </c>
-      <c r="C30" t="str">
-        <v>意识到</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="str">
-        <v>instruct</v>
-      </c>
-      <c r="C31" t="str">
-        <v>指示</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="str">
-        <v>rim</v>
-      </c>
-      <c r="C32" t="str">
-        <v>边缘</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="str">
-        <v>grain</v>
-      </c>
-      <c r="C33" t="str">
-        <v>谷物</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="str">
-        <v>stereo</v>
-      </c>
-      <c r="C34" t="str">
-        <v>音响</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="str">
-        <v>light</v>
-      </c>
-      <c r="C35" t="str">
-        <v>光</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
       <c r="B36" t="str">
-        <v>evade</v>
+        <v>/evade/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>躲避</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>multitude</v>
       </c>
       <c r="B37" t="str">
-        <v>multitude</v>
+        <v>/multitude/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>众多</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>fleet</v>
       </c>
       <c r="B38" t="str">
+        <v>/fleet/</v>
+      </c>
+      <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
+        <v>车队</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>explicit</v>
+      </c>
+      <c r="B39" t="str">
+        <v>/explicit/</v>
+      </c>
+      <c r="C39" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>详述的</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>spell</v>
+      </c>
+      <c r="B40" t="str">
+        <v>/spel/</v>
+      </c>
+      <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
+        <v>拼写</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>every</v>
+      </c>
+      <c r="B41" t="str">
+        <v>/every/</v>
+      </c>
+      <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
+        <v>每一个</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>marvelous</v>
+      </c>
+      <c r="B42" t="str">
+        <v>/marvelous/</v>
+      </c>
+      <c r="C42" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D42" t="str">
+        <v>惊人的</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>fitting</v>
+      </c>
+      <c r="B43" t="str">
+        <v>/fitting/</v>
+      </c>
+      <c r="C43" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D43" t="str">
+        <v>恰当的</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>layoff</v>
+      </c>
+      <c r="B44" t="str">
+        <v>/layoff/</v>
+      </c>
+      <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
+        <v>裁员</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>fraction</v>
+      </c>
+      <c r="B45" t="str">
+        <v>/fraction/</v>
+      </c>
+      <c r="C45" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D45" t="str">
+        <v>小部分</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>ski</v>
+      </c>
+      <c r="B46" t="str">
+        <v>/skiː/</v>
+      </c>
+      <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
+        <v>雪橇</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>paradigm</v>
+      </c>
+      <c r="B47" t="str">
+        <v>/paradigm/</v>
+      </c>
+      <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
+        <v>典范</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>over</v>
+      </c>
+      <c r="B48" t="str">
+        <v>/over/</v>
+      </c>
+      <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
+        <v>上方</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>return</v>
+      </c>
+      <c r="B49" t="str">
+        <v>/rɪˈtɜːn/</v>
+      </c>
+      <c r="C49" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D49" t="str">
+        <v>返回</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>on</v>
+      </c>
+      <c r="B50" t="str">
+        <v>/on/</v>
+      </c>
+      <c r="C50" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D50" t="str">
+        <v>向前</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>steam</v>
+      </c>
+      <c r="B51" t="str">
+        <v>/stiːm/</v>
+      </c>
+      <c r="C51" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D51" t="str">
+        <v>蒸汽</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>jog</v>
+      </c>
+      <c r="B52" t="str">
+        <v>/jog/</v>
+      </c>
+      <c r="C52" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D52" t="str">
+        <v>慢跑</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>because</v>
+      </c>
+      <c r="B53" t="str">
+        <v>/because/</v>
+      </c>
+      <c r="C53" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D53" t="str">
+        <v>因为</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
         <v>fleet</v>
       </c>
-      <c r="C38" t="str">
-        <v>车队</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>explicit</v>
-      </c>
-      <c r="C39" t="str">
-        <v>详述的</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>spell</v>
-      </c>
-      <c r="C40" t="str">
-        <v>拼写</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>every</v>
-      </c>
-      <c r="C41" t="str">
-        <v>每一个</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>marvelous</v>
-      </c>
-      <c r="C42" t="str">
-        <v>惊人的</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>fitting</v>
-      </c>
-      <c r="C43" t="str">
-        <v>恰当的</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>layoff</v>
-      </c>
-      <c r="C44" t="str">
-        <v>裁员</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>fraction</v>
-      </c>
-      <c r="C45" t="str">
-        <v>小部分</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>ski</v>
-      </c>
-      <c r="C46" t="str">
-        <v>雪橇</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>paradigm</v>
-      </c>
-      <c r="C47" t="str">
-        <v>典范</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
+      <c r="B54" t="str">
+        <v>/fleet/</v>
+      </c>
+      <c r="C54" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D54" t="str">
+        <v>舰队</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
         <v>over</v>
       </c>
-      <c r="C48" t="str">
-        <v>上方</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>return</v>
-      </c>
-      <c r="C49" t="str">
-        <v>返回</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>on</v>
-      </c>
-      <c r="C50" t="str">
-        <v>向前</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>steam</v>
-      </c>
-      <c r="C51" t="str">
-        <v>蒸汽</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>jog</v>
-      </c>
-      <c r="C52" t="str">
-        <v>慢跑</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>because</v>
-      </c>
-      <c r="C53" t="str">
-        <v>因为</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>fleet</v>
-      </c>
-      <c r="C54" t="str">
-        <v>舰队</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
       <c r="B55" t="str">
-        <v>over</v>
+        <v>/over/</v>
       </c>
       <c r="C55" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D55" t="str">
         <v>结束</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D55"/>
   </ignoredErrors>
 </worksheet>
 </file>